--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.20124616203286</v>
+        <v>8.320202501330339</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0088051380643</v>
+        <v>2.763930834935448</v>
       </c>
       <c r="E2" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F2" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.43038803651664</v>
+        <v>8.194938055933955</v>
       </c>
       <c r="D3" t="n">
-        <v>40.63800304486308</v>
+        <v>6.603675494790251</v>
       </c>
       <c r="E3" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F3" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.10182246415697</v>
+        <v>8.466546150425508</v>
       </c>
       <c r="D4" t="n">
-        <v>52.35466217013558</v>
+        <v>8.507632602647032</v>
       </c>
       <c r="E4" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F4" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.69756326307364</v>
+        <v>9.538354030249467</v>
       </c>
       <c r="D5" t="n">
-        <v>18.30132562260111</v>
+        <v>2.97396541367268</v>
       </c>
       <c r="E5" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F5" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.89384670778269</v>
+        <v>5.670250090014687</v>
       </c>
       <c r="D6" t="n">
-        <v>19.91682072055302</v>
+        <v>3.236483367089865</v>
       </c>
       <c r="E6" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F6" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.3116580703004</v>
+        <v>6.875644436423816</v>
       </c>
       <c r="D7" t="n">
-        <v>42.56332246951627</v>
+        <v>6.916539901296393</v>
       </c>
       <c r="E7" t="n">
-        <v>7.649615344034374</v>
+        <v>1.243062493405586</v>
       </c>
       <c r="F7" t="n">
-        <v>13.89638503351664</v>
+        <v>2.258162567946453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
